--- a/docx/Test case kiểm thử chức năng.xlsx
+++ b/docx/Test case kiểm thử chức năng.xlsx
@@ -8,19 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnTotNghiep_NguyenQuyen_10122312\docx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC554F5B-A753-42C8-A25B-5F41846B8FF0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159DF095-C80B-413C-B9DE-F14ABA13DE48}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190" tabRatio="455" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TC_DangNhap" sheetId="1" r:id="rId1"/>
     <sheet name="TC_DangKy" sheetId="2" r:id="rId2"/>
     <sheet name="TC_TimKiemSP" sheetId="4" r:id="rId3"/>
-    <sheet name="TC_ThanhToan" sheetId="6" r:id="rId4"/>
-    <sheet name="TC_SuaTT" sheetId="8" r:id="rId5"/>
+    <sheet name="Tổng hợp" sheetId="10" r:id="rId4"/>
+    <sheet name="TC_ThanhToan" sheetId="6" r:id="rId5"/>
+    <sheet name="TC_SuaTT" sheetId="8" r:id="rId6"/>
+    <sheet name="TC_E2E_MuaHang" sheetId="9" r:id="rId7"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="ACTION">#REF!</definedName>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="169">
   <si>
     <t>To Buglist</t>
   </si>
@@ -148,16 +150,10 @@
     <t>Đặt hàng thành công</t>
   </si>
   <si>
-    <t>Hệ thống không thông báo lỗi và cập nhật</t>
-  </si>
-  <si>
     <t>Bỏ trống sdt</t>
   </si>
   <si>
     <t>Bỏ trống họ tên</t>
-  </si>
-  <si>
-    <t>Hệ thống cập nhật thành công</t>
   </si>
   <si>
     <t xml:space="preserve">Expected Output 
@@ -322,14 +318,6 @@
   </si>
   <si>
     <t>xác nhận mật khẩu không khớp với mật khẩu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
-B2: Chọn chức năng đăng ký
-B3: Nhập email: ngminhtu@gmail
-B4: Nhập mật khẩu: ngminhtu
-B5: Nhập xác nhânh mật khẩu: ngminht
-B6: Nhấn "Đăng ký" </t>
   </si>
   <si>
     <t>Hiển thị trang chủ Ella
@@ -490,9 +478,6 @@
 </t>
   </si>
   <si>
-    <t>Hệ thống thông báo "Cập nhật thông tin tài khoản thành công"</t>
-  </si>
-  <si>
     <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
 B2: Đăng nhập tài khoản
 B3: Chọn Tài khoản
@@ -526,9 +511,6 @@
 </t>
   </si>
   <si>
-    <t>Số điện thoại &gt;10 số</t>
-  </si>
-  <si>
     <t>Số điện thoại &lt; 10 số</t>
   </si>
   <si>
@@ -551,12 +533,450 @@
 B7: Nhấn Cập nhật
 </t>
   </si>
+  <si>
+    <t>email thiếu trước @</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: @gmail.com
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: hoanganh@gmail.com
+B4: Nhập mật khẩu: hoanganh
+B5: Nhập xác nhânh mật khẩu: hoanganh1
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t>vị trí dấu '.' sai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://debac.vn/
+B2: Chọn chức năng đăng ký
+B3: Nhập email: ngminhtu@gmail.
+B4: Nhập mật khẩu: ngminhtu
+B5: Nhập xác nhânh mật khẩu: ngminhtu
+B6: Nhấn "Đăng ký" </t>
+  </si>
+  <si>
+    <t>Hiển thị trang chủ Ella
+Hiển thị giao diện đăng ký
+Thông báo lỗi "'.' bị sử dụng sai vị trí trong '.' "</t>
+  </si>
+  <si>
+    <t>Hiển thị trang chủ Ella
+Hiển thị giao diện đăng ký
+Thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t>register_Auto_Test_3_20260519_001508.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 01234
+B6: Nhập email: linhnguyen@gmail.com
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 012345679@
+B6: Nhập email: linhnguyen@gmail.com
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t>Email thiếu phần sau @</t>
+  </si>
+  <si>
+    <t>Email thiếu phần trước @</t>
+  </si>
+  <si>
+    <t>Email thiếu @</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 0123456789
+B6: Nhập email: linhnguyen@
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 0123456789
+B6: Nhập email: @gmail.com
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 0123456789
+B6: Nhập email: linhnguyen@gmail.
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 0123456789
+B6: Nhập email: linhnguyengmail
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
+  </si>
+  <si>
+    <t>Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
+  </si>
+  <si>
+    <t>order_Auto_Test_3_20260515_165252.png</t>
+  </si>
+  <si>
+    <t>Số điện thoại chứa ký tự đặc biệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Chọn Tài khoản
+B4: Nhập Họ và tên: Hoang Nguyen
+B5: Nhập SDT: 012345678@
+B6: Địa chỉ: 123 Main St, Hanoi
+B7: Nhấn Cập nhật
+</t>
+  </si>
+  <si>
+    <t>Số điện thoại &gt; 10 số</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Chọn Tài khoản
+B4: Nhập Họ và tên: Hoang Nguyen
+B5: Nhập SDT: 012345678aa
+B6: Địa chỉ: 123 Main St, Hanoi
+B7: Nhấn Cập nhật
+</t>
+  </si>
+  <si>
+    <t>Số điện thoại chứa chữ</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_5_.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_6.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_7.png</t>
+  </si>
+  <si>
+    <t>E2E_login_20260517_213426_8.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 01234
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 012345678999
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 012345679@
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: linhnguyen@
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: @gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: linhnguyengmail
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 0123456789
+B8: Nhập email: linhnguyen@gmail.
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chức năng </t>
+  </si>
+  <si>
+    <t>Đăng ký</t>
+  </si>
+  <si>
+    <t>Đăng nhập</t>
+  </si>
+  <si>
+    <t>Tìm kiếm</t>
+  </si>
+  <si>
+    <t>Đặt hàng</t>
+  </si>
+  <si>
+    <t>E2E Đặt hàng</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Sai số điện thoại chứa chữ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Đăng nhập tài khoản
+B3: Tim kiếm sản phẩm
+B4: Chọn sản phẩm
+B5: Chọn "Thêm vào giỏ"
+B6: Nhập họ tên: Linh
+B7: Nhập Số điện thoại: 012345679a
+B8: Nhập email: linhnguyen@gmail.com
+B9: Nhập địa chỉ: 123 Main St, City
+B10: Nhập ghi chú: Giao giờ hành chính
+B11: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1: Truy cập vào website https://ella.vn/
+B2: Chọn sản phẩm
+B3: Chọn "Thêm vào giỏ"
+B4: Nhập họ tên: Linh
+B5: Nhập Số điện thoại: 012345679a
+B6: Nhập email: linhnguyen@gmail.com
+B7: Nhập địa chỉ: 123 Main St, City
+B8: Nhập ghi chú: Giao giờ hành chính
+B9: Nhấn "Thanh toán" 
+</t>
+  </si>
+  <si>
+    <t>Số lượng kịch bản</t>
+  </si>
+  <si>
+    <t>Tổng số</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Đơn hàng của bạn đã được gửi đi"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng điền vào trường này"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng nhập phần đứng sau @"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng nhập phần đứng trước @"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng nhập bao gồm '@' trong địa chỉ email"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "'.' bị sai vị trí trong '.'"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "Vui lòng"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Tìm kiếm đúng sản phẩm
+Hệ thống thông báo "sai vị trí"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Hệ thống thông báo "Cập nhật thông tin tài khoản thành công"</t>
+  </si>
+  <si>
+    <t>Đăng nhập thành công
+Hệ thống thông báo "Vui lòng nhập ít nhất một số điện thoại bạn đang sử dụng"</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -624,8 +1044,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -652,12 +1078,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -730,19 +1180,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -750,7 +1187,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -792,9 +1229,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -838,16 +1272,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -857,7 +1285,35 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1203,7 +1659,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1214,9 +1670,9 @@
         <f>"Pass: "&amp;COUNTIF(G5:G9,"Pass")</f>
         <v>Pass: 5</v>
       </c>
-      <c r="E1" s="6" t="e">
-        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
-        <v>#REF!</v>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G9,"Untest")</f>
+        <v>Untested: 0</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -1234,27 +1690,27 @@
         <f>"Fail: "&amp;COUNTIF(G5:G6,"Fail")</f>
         <v>Fail: 0</v>
       </c>
-      <c r="E2" s="6" t="e">
-        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
-        <v>#REF!</v>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G9,"N/A")</f>
+        <v>N/A: 0</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="e">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$963)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="23" t="str">
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(G5:G9,"Pass")*100)/((COUNTA($A$5:$A$9))-COUNTIF(G5:G9,"N/A")),2)&amp;"%"</f>
+        <v>Percent Complete: 100%</v>
+      </c>
+      <c r="E3" s="22" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$9))</f>
         <v>Number of cases: 5</v>
       </c>
@@ -1263,163 +1719,163 @@
       <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="28.4" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="50.25" customHeight="1">
-      <c r="A5" s="25" t="str">
+      <c r="A5" s="24" t="str">
         <f>"[DangNhap - " &amp; TEXT(ROW(A1), "00") &amp; "]"</f>
         <v>[DangNhap - 01]</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="27" t="s">
+      <c r="D5" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="50">
-      <c r="A6" s="25" t="str">
+      <c r="A6" s="24" t="str">
         <f t="shared" ref="A6:A9" si="0">"[DangNhap - " &amp; TEXT(ROW(A2), "00") &amp; "]"</f>
         <v>[DangNhap - 02]</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="27" t="s">
+      <c r="D6" s="19" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="50">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 03]</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="27" t="s">
+      <c r="D7" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="50">
-      <c r="A8" s="25" t="str">
+      <c r="A8" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 04]</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="27" t="s">
+      <c r="D8" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="26" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="50">
-      <c r="A9" s="25" t="str">
+      <c r="A9" s="24" t="str">
         <f t="shared" si="0"/>
         <v>[DangNhap - 05]</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="27" t="s">
+      <c r="D9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1460,7 +1916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21EF83A7-E3CF-42CA-A136-CBA0E91CF224}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="10"/>
   <cols>
     <col min="1" max="1" width="12" style="1" customWidth="1"/>
@@ -1475,7 +1931,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1483,12 +1939,12 @@
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="str">
-        <f>"Pass: "&amp;COUNTIF(G5:G12,"Pass")</f>
-        <v>Pass: 7</v>
-      </c>
-      <c r="E1" s="6" t="e">
-        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
-        <v>#REF!</v>
+        <f>"Pass: "&amp;COUNTIF(G5:G14,"Pass")</f>
+        <v>Pass: 9</v>
+      </c>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G14,"Untest")</f>
+        <v>Untested: 0</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -1503,294 +1959,356 @@
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5" t="str">
-        <f>"Fail: "&amp;COUNTIF(G5:G12,"Fail")</f>
+        <f>"Fail: "&amp;COUNTIF(G5:G13,"Fail")</f>
         <v>Fail: 1</v>
       </c>
-      <c r="E2" s="6" t="e">
-        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
-        <v>#REF!</v>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G14,"N/A")</f>
+        <v>N/A: 0</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="e">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$959)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="23" t="str">
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(G5:G14,"Pass")*100)/((COUNTA($A$5:$A$14))-COUNTIF(G5:G14,"N/A")),2)&amp;"%"</f>
+        <v>Percent Complete: 90%</v>
+      </c>
+      <c r="E3" s="22" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$959))</f>
-        <v>Number of cases: 8</v>
+        <v>Number of cases: 10</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:9" ht="28.4" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="5" spans="1:9" s="2" customFormat="1" ht="60">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f>"[DangKy - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[DangKy - 01]</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="28" t="s">
-        <v>20</v>
-      </c>
+      <c r="D5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="36"/>
     </row>
     <row r="6" spans="1:9" ht="60">
-      <c r="A6" s="20" t="str">
-        <f t="shared" ref="A6:A12" si="0">"[DangKy - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
+      <c r="A6" s="19" t="str">
+        <f t="shared" ref="A6:A7" si="0">"[DangKy - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[DangKy - 02]</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>20</v>
-      </c>
+      <c r="D6" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="37"/>
     </row>
     <row r="7" spans="1:9" ht="60">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[DangKy - 03]</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60">
+      <c r="A8" s="19" t="str">
+        <f>"[DangKy - " &amp; TEXT(ROW(A4),"00") &amp; "]"</f>
+        <v>[DangKy - 04]</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="37"/>
+    </row>
+    <row r="9" spans="1:9" ht="60">
+      <c r="A9" s="19" t="str">
+        <f>"[DangKy - " &amp; TEXT(ROW(A5),"00") &amp; "]"</f>
+        <v>[DangKy - 05]</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C9" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="37"/>
+    </row>
+    <row r="10" spans="1:9" ht="60">
+      <c r="A10" s="19" t="str">
+        <f>"[DangKy - " &amp; TEXT(ROW(A7),"00") &amp; "]"</f>
+        <v>[DangKy - 07]</v>
+      </c>
+      <c r="B10" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="60">
-      <c r="A8" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>[DangKy - 04]</v>
-      </c>
-      <c r="B8" s="26" t="s">
+      <c r="C10" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="37"/>
+    </row>
+    <row r="11" spans="1:9" ht="60">
+      <c r="A11" s="19" t="str">
+        <f>"[DangKy - " &amp; TEXT(ROW(A6),"00") &amp; "]"</f>
+        <v>[DangKy - 06]</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="E11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="34"/>
+    </row>
+    <row r="12" spans="1:9" ht="60">
+      <c r="A12" s="19" t="str">
+        <f t="shared" ref="A12:A14" si="1">"[DangKy - " &amp; TEXT(ROW(A8),"00") &amp; "]"</f>
+        <v>[DangKy - 08]</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="60">
-      <c r="A9" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>[DangKy - 05]</v>
-      </c>
-      <c r="B9" s="26" t="s">
+      <c r="D12" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="F12" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="34"/>
+    </row>
+    <row r="13" spans="1:9" ht="68" customHeight="1">
+      <c r="A13" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>[DangKy - 09]</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="16"/>
-    </row>
-    <row r="10" spans="1:9" ht="60">
-      <c r="A10" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>[DangKy - 06]</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="D13" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="37"/>
+    </row>
+    <row r="14" spans="1:9" ht="68" customHeight="1">
+      <c r="A14" s="19" t="str">
+        <f t="shared" si="1"/>
+        <v>[DangKy - 10]</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="16"/>
-    </row>
-    <row r="11" spans="1:9" ht="60">
-      <c r="A11" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>[DangKy - 07]</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="60">
-      <c r="A12" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v>[DangKy - 08]</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="F12" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="28" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="31"/>
+      <c r="D14" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="37"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" location="BugList!A1" display="To Buglist" xr:uid="{B79BF084-50C5-49A5-A50F-92D6680D8D1C}"/>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{3852A2AE-6ED2-4C3E-BA7A-5A6CF7C7E9F0}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{6ECDF2A3-A60F-476B-9EEC-0F76C77BC890}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -1810,7 +2328,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -1821,9 +2339,9 @@
         <f>"Pass: "&amp;COUNTIF(G5:G15,"Pass")</f>
         <v>Pass: 6</v>
       </c>
-      <c r="E1" s="6" t="e">
-        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
-        <v>#REF!</v>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G10,"Untest")</f>
+        <v>Untested: 0</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -1840,26 +2358,26 @@
         <f>"Fail: "&amp;COUNTIF(G5:G15,"Fail")</f>
         <v>Fail: 0</v>
       </c>
-      <c r="E2" s="6" t="e">
-        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
-        <v>#REF!</v>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G10,"N/A")</f>
+        <v>N/A: 0</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
     <row r="3" spans="1:9" ht="12.75" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="e">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$965)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="23" t="str">
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;ROUND((COUNTIF(G5:G10,"Pass")*100)/((COUNTA($A$5:$A$10))-COUNTIF(G5:G10,"N/A")),2)&amp;"%"</f>
+        <v>Percent Complete: 100%</v>
+      </c>
+      <c r="E3" s="22" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$965))</f>
         <v>Number of cases: 6</v>
       </c>
@@ -1867,196 +2385,196 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:9" ht="28.4" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="30" t="s">
-        <v>41</v>
+      <c r="I4" s="29" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="15" customFormat="1" ht="50">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f>"[TimKiemSP - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[TimKiemSP - 01]</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="35" t="s">
+      <c r="D5" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="50">
-      <c r="A6" s="20" t="str">
+      <c r="A6" s="19" t="str">
         <f t="shared" ref="A6:A10" si="0">"[TimKiemSP - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[TimKiemSP - 02]</v>
       </c>
-      <c r="B6" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="35" t="s">
+      <c r="D6" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="32" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="60">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 03]</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="17"/>
+      <c r="D7" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" ht="50">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="19" t="str">
         <f>"[TimKiemSP - " &amp; TEXT(ROW(C4),"00") &amp; "]"</f>
         <v>[TimKiemSP - 04]</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="18"/>
+      <c r="D8" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="17"/>
     </row>
     <row r="9" spans="1:9" ht="50">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 05]</v>
       </c>
-      <c r="B9" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="17"/>
+      <c r="D9" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="16"/>
     </row>
     <row r="10" spans="1:9" ht="50">
-      <c r="A10" s="20" t="str">
+      <c r="A10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[TimKiemSP - 06]</v>
       </c>
-      <c r="B10" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="35" t="s">
+      <c r="D10" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="32" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2091,8 +2609,139 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A55E798-73C5-4916-82B2-E9D7D7546E22}">
+  <dimension ref="F4:I11"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="8.26953125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="6:9" ht="14.5">
+      <c r="F4" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9" ht="14.5">
+      <c r="F5" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="41">
+        <v>10</v>
+      </c>
+      <c r="H5" s="41">
+        <v>9</v>
+      </c>
+      <c r="I5" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="6:9" ht="14.5">
+      <c r="F6" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="G6" s="46">
+        <v>5</v>
+      </c>
+      <c r="H6" s="46">
+        <v>5</v>
+      </c>
+      <c r="I6" s="46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="6:9" ht="14.5">
+      <c r="F7" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="G7" s="41">
+        <v>6</v>
+      </c>
+      <c r="H7" s="41">
+        <v>6</v>
+      </c>
+      <c r="I7" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="6:9" ht="14.5">
+      <c r="F8" s="45" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="46">
+        <v>11</v>
+      </c>
+      <c r="H8" s="46">
+        <v>10</v>
+      </c>
+      <c r="I8" s="46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="6:9" ht="14.5">
+      <c r="F9" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="G9" s="41">
+        <v>11</v>
+      </c>
+      <c r="H9" s="41">
+        <v>10</v>
+      </c>
+      <c r="I9" s="41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="6:9" ht="14.5">
+      <c r="F10" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="G10" s="46">
+        <v>8</v>
+      </c>
+      <c r="H10" s="46">
+        <v>4</v>
+      </c>
+      <c r="I10" s="46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="6:9" ht="14.5">
+      <c r="F11" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="44">
+        <f>SUM(G5:G10)</f>
+        <v>51</v>
+      </c>
+      <c r="H11" s="42">
+        <f t="shared" ref="H11:I11" si="0">SUM(H5:H10)</f>
+        <v>44</v>
+      </c>
+      <c r="I11" s="47">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93ED25E9-734E-4BB9-B6DD-ADDDAEBE5EA0}">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
@@ -2106,7 +2755,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -2114,12 +2763,12 @@
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="str">
-        <f>"Pass: "&amp;COUNTIF(G5:G9,"Pass")</f>
-        <v>Pass: 4</v>
-      </c>
-      <c r="E1" s="6" t="e">
-        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
-        <v>#REF!</v>
+        <f>"Pass: "&amp;COUNTIF(G5:G15,"Pass")</f>
+        <v>Pass: 10</v>
+      </c>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G15,"Untest")</f>
+        <v>Untested: 0</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -2134,222 +2783,390 @@
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5" t="str">
-        <f>"Fail: "&amp;COUNTIF(G5:G9,"Fail")</f>
+        <f>"Fail: "&amp;COUNTIF(G5:G15,"Fail")</f>
         <v>Fail: 1</v>
       </c>
-      <c r="E2" s="6" t="e">
-        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
-        <v>#REF!</v>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G15,"N/A")</f>
+        <v>N/A: 0</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="e">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$958)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="23" t="str">
-        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$958))</f>
-        <v>Number of cases: 5</v>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;IFERROR(ROUND((COUNTIF(G5:G15,"Pass")*100)/(COUNTA(G5:G15)-COUNTIF(G5:G15,"N/A")),2),0)&amp;"%"</f>
+        <v>Percent Complete: 90.91%</v>
+      </c>
+      <c r="E3" s="22" t="str">
+        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$959))</f>
+        <v>Number of cases: 11</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="36.5" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>41</v>
+      <c r="I4" s="23" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="100">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f>"[ThanhToan - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[ThanhToan - 01]</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="36"/>
+      <c r="D5" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="33"/>
     </row>
     <row r="6" spans="1:9" ht="100">
-      <c r="A6" s="20" t="str">
-        <f t="shared" ref="A6:A9" si="0">"[ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
+      <c r="A6" s="19" t="str">
+        <f t="shared" ref="A6:A15" si="0">"[ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[ThanhToan - 02]</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="20" t="s">
+      <c r="D6" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="F6" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="G6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="36"/>
+      <c r="G6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="33"/>
     </row>
     <row r="7" spans="1:9" ht="100">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 03]</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="20" t="s">
+      <c r="D7" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="36"/>
+      <c r="F7" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="100">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 04]</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="36"/>
+      <c r="D8" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="33"/>
     </row>
     <row r="9" spans="1:9" ht="100">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ThanhToan - 05]</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="33"/>
+    </row>
+    <row r="10" spans="1:9" ht="100">
+      <c r="A10" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 06]</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="36"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="B10" s="31"/>
+      <c r="F10" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="1:9" ht="100">
+      <c r="A11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 07]</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="33"/>
+    </row>
+    <row r="12" spans="1:9" ht="100">
+      <c r="A12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 08]</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:9" ht="100">
+      <c r="A13" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 09]</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="1:9" ht="100">
+      <c r="A14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 10]</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="33"/>
+    </row>
+    <row r="15" spans="1:9" ht="100">
+      <c r="A15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 11]</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="33"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" location="BugList!A1" display="To Buglist" xr:uid="{07606E3B-9B4E-48B7-85EB-5B0C6571987F}"/>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{8E4886B0-4173-410D-9DE8-436F22B7FC57}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{0057FB9B-9334-481E-B37D-13888CFB828B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB8945F8-44BD-40EB-BEFA-56F152ECC625}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -2362,7 +3179,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.5">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="18" t="s">
         <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -2370,12 +3187,12 @@
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="5" t="str">
-        <f>"Pass: "&amp;COUNTIF(G5:G10,"Pass")</f>
+        <f>"Pass: "&amp;COUNTIF(G5:G12,"Pass")</f>
         <v>Pass: 4</v>
       </c>
-      <c r="E1" s="6" t="e">
-        <f>"Untested: "&amp;COUNTIF(#REF!,"Untest")</f>
-        <v>#REF!</v>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G14,"Untest")</f>
+        <v>Untested: 0</v>
       </c>
       <c r="F1" s="7"/>
       <c r="G1" s="7"/>
@@ -2390,244 +3207,730 @@
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="5" t="str">
-        <f>"Fail: "&amp;COUNTIF(G5:G10,"Fail")</f>
-        <v>Fail: 2</v>
-      </c>
-      <c r="E2" s="6" t="e">
-        <f>"N/A: "&amp;COUNTIF(#REF!,"N/A")</f>
-        <v>#REF!</v>
+        <f>"Fail: "&amp;COUNTIF(G5:G12,"Fail")</f>
+        <v>Fail: 4</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G14,"N/A")</f>
+        <v>N/A: 0</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:9" ht="20">
+      <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="e">
-        <f>"Percent Complete: "&amp;ROUND((COUNTIF(#REF!,"Pass")*100)/((COUNTA($A$5:$A$964)*5)-COUNTIF(#REF!,"N/A")),2)&amp;"%"</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E3" s="23" t="str">
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;IFERROR(ROUND((COUNTIF(G5:G12,"Pass")*100)/(COUNTA(G5:G12)-COUNTIF(G5:G12,"N/A")),2),0)&amp;"%"</f>
+        <v>Percent Complete: 50%</v>
+      </c>
+      <c r="E3" s="22" t="str">
         <f>"Number of cases: "&amp;(COUNTA($A$5:$A$964))</f>
-        <v>Number of cases: 6</v>
+        <v>Number of cases: 8</v>
       </c>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="8"/>
     </row>
     <row r="4" spans="1:9" ht="20">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="I4" s="24" t="s">
-        <v>41</v>
+      <c r="I4" s="23" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="80">
-      <c r="A5" s="20" t="str">
+      <c r="A5" s="19" t="str">
         <f>"[ChangeProfile - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
         <v>[ChangeProfile - 01]</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="33" t="s">
+      <c r="B5" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="37"/>
+      <c r="D5" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="34"/>
     </row>
     <row r="6" spans="1:9" ht="80">
-      <c r="A6" s="20" t="str">
-        <f t="shared" ref="A6:A10" si="0">"[ChangeProfile - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
+      <c r="A6" s="19" t="str">
+        <f t="shared" ref="A6:A12" si="0">"[ChangeProfile - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
         <v>[ChangeProfile - 02]</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="33" t="s">
+      <c r="B6" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="37"/>
+      <c r="D6" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="34"/>
     </row>
     <row r="7" spans="1:9" ht="80">
-      <c r="A7" s="20" t="str">
+      <c r="A7" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 03]</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="33" t="s">
+      <c r="B7" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="37"/>
+      <c r="D7" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="34"/>
     </row>
     <row r="8" spans="1:9" ht="80">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 04]</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="33" t="s">
+      <c r="B8" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I8" s="37"/>
+      <c r="D8" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="34"/>
     </row>
     <row r="9" spans="1:9" ht="80">
-      <c r="A9" s="20" t="str">
+      <c r="A9" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 05]</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="20" t="s">
+      <c r="D9" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I9" s="38"/>
+      <c r="H9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="80">
-      <c r="A10" s="20" t="str">
+      <c r="A10" s="19" t="str">
         <f t="shared" si="0"/>
         <v>[ChangeProfile - 06]</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>104</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="B10" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="G10" s="20" t="s">
+      <c r="D10" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G10" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="38"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="31"/>
-      <c r="D11" s="12"/>
-      <c r="G11" s="31"/>
-      <c r="H11" s="31"/>
+      <c r="H10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="80">
+      <c r="A11" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ChangeProfile - 07]</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G11" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="80">
+      <c r="A12" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ChangeProfile - 08]</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="G12" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>135</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B1" location="BugList!A1" display="To Buglist" xr:uid="{6F980733-6528-424B-B45A-75D8EB680571}"/>
     <hyperlink ref="A1" r:id="rId1" xr:uid="{79014417-D33A-48E5-ABCD-22679886FC3B}"/>
+    <hyperlink ref="I9" r:id="rId2" display="..\screenshots\E2E_login_20260517_213426_5_20260519_030532.png" xr:uid="{24F2C39C-A2BF-4E1D-BEC4-DB37E8FBD3D9}"/>
+    <hyperlink ref="I10" r:id="rId3" xr:uid="{E5BA72D2-91F9-470C-A182-B694505EAA04}"/>
+    <hyperlink ref="I11" r:id="rId4" xr:uid="{AE3A4F13-1BDE-4CB0-852A-ED458A6944D6}"/>
+    <hyperlink ref="I12" r:id="rId5" xr:uid="{B9092595-C182-4014-8309-32004122821E}"/>
+    <hyperlink ref="I9:I12" r:id="rId6" display="E2E_login_20260517_213426_5_.png" xr:uid="{AA14C026-3BC7-4CAE-A88E-E9CEB146D70C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9DC36A3-A34C-4DBA-AF2D-BF8F96A0B921}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="13"/>
+  <cols>
+    <col min="1" max="1" width="11.6328125" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="28.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.54296875" customWidth="1"/>
+    <col min="6" max="6" width="18.6328125" customWidth="1"/>
+    <col min="7" max="7" width="5.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.5">
+      <c r="A1" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5" t="str">
+        <f>"Pass: "&amp;COUNTIF(G5:G15,"Pass")</f>
+        <v>Pass: 10</v>
+      </c>
+      <c r="E1" s="6" t="str">
+        <f>"Untested: "&amp;COUNTIF(G5:G15,"Untest")</f>
+        <v>Untested: 0</v>
+      </c>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="5" t="str">
+        <f>"Fail: "&amp;COUNTIF(G5:G15,"Fail")</f>
+        <v>Fail: 1</v>
+      </c>
+      <c r="E2" s="6" t="str">
+        <f>"N/A: "&amp;COUNTIF(G5:G15,"N/A")</f>
+        <v>N/A: 0</v>
+      </c>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:9" ht="20">
+      <c r="A3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21" t="str">
+        <f>"Percent Complete: "&amp;IFERROR(ROUND((COUNTIF(G5:G15,"Pass")*100)/(COUNTA(G5:G15)-COUNTIF(G5:G15,"N/A")),2),0)&amp;"%"</f>
+        <v>Percent Complete: 90.91%</v>
+      </c>
+      <c r="E3" s="22" t="str">
+        <f>"Number of cases: "&amp;(COUNTA($A$5:$A$959))</f>
+        <v>Number of cases: 11</v>
+      </c>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:9" ht="20">
+      <c r="A4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="120">
+      <c r="A5" s="19" t="str">
+        <f>"[ThanhToan - " &amp; TEXT(ROW(A1),"00") &amp; "]"</f>
+        <v>[ThanhToan - 01]</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="33"/>
+    </row>
+    <row r="6" spans="1:9" ht="120">
+      <c r="A6" s="19" t="str">
+        <f t="shared" ref="A6:A15" si="0">"[ThanhToan - " &amp; TEXT(ROW(A2),"00") &amp; "]"</f>
+        <v>[ThanhToan - 02]</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="33"/>
+    </row>
+    <row r="7" spans="1:9" ht="120">
+      <c r="A7" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 03]</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="120">
+      <c r="A8" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 04]</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="33"/>
+    </row>
+    <row r="9" spans="1:9" ht="120">
+      <c r="A9" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 05]</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" s="33"/>
+    </row>
+    <row r="10" spans="1:9" ht="120">
+      <c r="A10" s="19" t="str">
+        <f>"[ThanhToan - " &amp; TEXT(ROW(A5),"00") &amp; "]"</f>
+        <v>[ThanhToan - 05]</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="33"/>
+    </row>
+    <row r="11" spans="1:9" ht="120">
+      <c r="A11" s="19" t="str">
+        <f>"[ThanhToan - " &amp; TEXT(ROW(A6),"00") &amp; "]"</f>
+        <v>[ThanhToan - 06]</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I11" s="33"/>
+    </row>
+    <row r="12" spans="1:9" ht="120">
+      <c r="A12" s="19" t="str">
+        <f>"[ThanhToan - " &amp; TEXT(ROW(A7),"00") &amp; "]"</f>
+        <v>[ThanhToan - 07]</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="33"/>
+    </row>
+    <row r="13" spans="1:9" ht="120">
+      <c r="A13" s="19" t="str">
+        <f>"[ThanhToan - " &amp; TEXT(ROW(A8),"00") &amp; "]"</f>
+        <v>[ThanhToan - 08]</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="33"/>
+    </row>
+    <row r="14" spans="1:9" ht="120">
+      <c r="A14" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 10]</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E14" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F14" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="33"/>
+    </row>
+    <row r="15" spans="1:9" ht="120">
+      <c r="A15" s="19" t="str">
+        <f t="shared" si="0"/>
+        <v>[ThanhToan - 11]</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="F15" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G15" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="33"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B1" location="BugList!A1" display="To Buglist" xr:uid="{40AD8936-CBB9-4362-A17D-56DF430C38DE}"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{BFD4DF51-BA15-4F62-A431-6076A5C1829F}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{76EFCAE4-3F8D-465B-B672-68EBF140DE33}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
